--- a/artfynd/A 24424-2026 artfynd.xlsx
+++ b/artfynd/A 24424-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2713,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134665132</v>
+        <v>134665114</v>
       </c>
       <c r="B21" t="n">
-        <v>91896</v>
+        <v>92027</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,21 +2724,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518871</v>
+        <v>519025</v>
       </c>
       <c r="R21" t="n">
-        <v>6906465</v>
+        <v>6906429</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2802,6 +2802,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2820,10 +2821,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134665104</v>
+        <v>134665132</v>
       </c>
       <c r="B22" t="n">
-        <v>93271</v>
+        <v>91896</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2831,21 +2832,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,13 +2856,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518929</v>
+        <v>518871</v>
       </c>
       <c r="R22" t="n">
-        <v>6906496</v>
+        <v>6906465</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2890,7 +2891,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2900,7 +2901,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2927,7 +2928,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134665105</v>
+        <v>134665104</v>
       </c>
       <c r="B23" t="n">
         <v>93271</v>
@@ -2962,13 +2963,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518942</v>
+        <v>518929</v>
       </c>
       <c r="R23" t="n">
-        <v>6906487</v>
+        <v>6906496</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2997,7 +2998,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3007,7 +3008,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,32 +3035,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134665039</v>
+        <v>134665105</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3069,13 +3070,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518782</v>
+        <v>518942</v>
       </c>
       <c r="R24" t="n">
-        <v>6906438</v>
+        <v>6906487</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3104,7 +3105,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3114,7 +3115,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,7 +3142,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134665069</v>
+        <v>134665039</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3176,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518832</v>
+        <v>518782</v>
       </c>
       <c r="R25" t="n">
-        <v>6906410</v>
+        <v>6906438</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3211,7 +3212,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3221,7 +3222,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,7 +3249,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134665101</v>
+        <v>134665069</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3283,13 +3284,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518918</v>
+        <v>518832</v>
       </c>
       <c r="R26" t="n">
-        <v>6906430</v>
+        <v>6906410</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3318,7 +3319,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3328,7 +3329,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3355,7 +3356,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134665103</v>
+        <v>134665101</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3390,13 +3391,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518929</v>
+        <v>518918</v>
       </c>
       <c r="R27" t="n">
-        <v>6906443</v>
+        <v>6906430</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3425,7 +3426,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3435,7 +3436,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3462,7 +3463,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134665109</v>
+        <v>134665103</v>
       </c>
       <c r="B28" t="n">
         <v>79373</v>
@@ -3497,10 +3498,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518992</v>
+        <v>518929</v>
       </c>
       <c r="R28" t="n">
-        <v>6906517</v>
+        <v>6906443</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3532,7 +3533,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3542,7 +3543,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3569,7 +3570,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134665111</v>
+        <v>134665109</v>
       </c>
       <c r="B29" t="n">
         <v>79373</v>
@@ -3604,10 +3605,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519059</v>
+        <v>518992</v>
       </c>
       <c r="R29" t="n">
-        <v>6906455</v>
+        <v>6906517</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3639,7 +3640,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3649,7 +3650,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3676,7 +3677,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134665115</v>
+        <v>134665111</v>
       </c>
       <c r="B30" t="n">
         <v>79373</v>
@@ -3711,13 +3712,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519011</v>
+        <v>519059</v>
       </c>
       <c r="R30" t="n">
-        <v>6906409</v>
+        <v>6906455</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3746,7 +3747,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3756,7 +3757,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3783,32 +3784,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134665041</v>
+        <v>134665115</v>
       </c>
       <c r="B31" t="n">
-        <v>83341</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3818,13 +3819,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518791</v>
+        <v>519011</v>
       </c>
       <c r="R31" t="n">
-        <v>6906427</v>
+        <v>6906409</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3853,7 +3854,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3863,7 +3864,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3890,32 +3891,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134665045</v>
+        <v>134665041</v>
       </c>
       <c r="B32" t="n">
-        <v>83358</v>
+        <v>83341</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3926,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518806</v>
+        <v>518791</v>
       </c>
       <c r="R32" t="n">
-        <v>6906421</v>
+        <v>6906427</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3960,7 +3961,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3970,7 +3971,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3997,7 +3998,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134665106</v>
+        <v>134665045</v>
       </c>
       <c r="B33" t="n">
         <v>83358</v>
@@ -4032,10 +4033,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518975</v>
+        <v>518806</v>
       </c>
       <c r="R33" t="n">
-        <v>6906484</v>
+        <v>6906421</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4067,7 +4068,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4077,7 +4078,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4104,10 +4105,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134665108</v>
+        <v>134665106</v>
       </c>
       <c r="B34" t="n">
-        <v>79130</v>
+        <v>83358</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4115,21 +4116,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4139,13 +4140,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518993</v>
+        <v>518975</v>
       </c>
       <c r="R34" t="n">
-        <v>6906512</v>
+        <v>6906484</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4174,7 +4175,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4184,7 +4185,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4211,7 +4212,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134665112</v>
+        <v>134665108</v>
       </c>
       <c r="B35" t="n">
         <v>79130</v>
@@ -4246,10 +4247,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519043</v>
+        <v>518993</v>
       </c>
       <c r="R35" t="n">
-        <v>6906438</v>
+        <v>6906512</v>
       </c>
       <c r="S35" t="n">
         <v>6</v>
@@ -4281,7 +4282,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4291,7 +4292,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4318,32 +4319,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134665037</v>
+        <v>134665112</v>
       </c>
       <c r="B36" t="n">
-        <v>80382</v>
+        <v>79130</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4353,13 +4354,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518772</v>
+        <v>519043</v>
       </c>
       <c r="R36" t="n">
-        <v>6906427</v>
+        <v>6906438</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4388,7 +4389,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4398,7 +4399,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4425,32 +4426,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134665035</v>
+        <v>134665037</v>
       </c>
       <c r="B37" t="n">
-        <v>80488</v>
+        <v>80382</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4460,10 +4461,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518771</v>
+        <v>518772</v>
       </c>
       <c r="R37" t="n">
-        <v>6906422</v>
+        <v>6906427</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4495,7 +4496,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4505,7 +4506,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4532,7 +4533,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134665065</v>
+        <v>134665035</v>
       </c>
       <c r="B38" t="n">
         <v>80488</v>
@@ -4567,10 +4568,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518823</v>
+        <v>518771</v>
       </c>
       <c r="R38" t="n">
-        <v>6906410</v>
+        <v>6906422</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4602,7 +4603,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4612,7 +4613,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4639,7 +4640,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134665083</v>
+        <v>134665065</v>
       </c>
       <c r="B39" t="n">
         <v>80488</v>
@@ -4674,10 +4675,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518842</v>
+        <v>518823</v>
       </c>
       <c r="R39" t="n">
-        <v>6906433</v>
+        <v>6906410</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4709,7 +4710,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4719,12 +4720,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:36</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4751,7 +4747,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134665122</v>
+        <v>134665083</v>
       </c>
       <c r="B40" t="n">
         <v>80488</v>
@@ -4786,13 +4782,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518913</v>
+        <v>518842</v>
       </c>
       <c r="R40" t="n">
-        <v>6906330</v>
+        <v>6906433</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4821,7 +4817,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4831,7 +4827,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4858,7 +4859,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134665126</v>
+        <v>134665122</v>
       </c>
       <c r="B41" t="n">
         <v>80488</v>
@@ -4893,10 +4894,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518876</v>
+        <v>518913</v>
       </c>
       <c r="R41" t="n">
-        <v>6906381</v>
+        <v>6906330</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,7 +4929,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4938,7 +4939,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4965,32 +4966,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134665063</v>
+        <v>134665126</v>
       </c>
       <c r="B42" t="n">
-        <v>80493</v>
+        <v>80488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5000,13 +5001,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518823</v>
+        <v>518876</v>
       </c>
       <c r="R42" t="n">
-        <v>6906413</v>
+        <v>6906381</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5035,7 +5036,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5045,7 +5046,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5072,7 +5073,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134665121</v>
+        <v>134665063</v>
       </c>
       <c r="B43" t="n">
         <v>80493</v>
@@ -5107,13 +5108,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518919</v>
+        <v>518823</v>
       </c>
       <c r="R43" t="n">
-        <v>6906309</v>
+        <v>6906413</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5142,7 +5143,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5152,7 +5153,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5179,7 +5180,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134665124</v>
+        <v>134665121</v>
       </c>
       <c r="B44" t="n">
         <v>80493</v>
@@ -5214,13 +5215,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518888</v>
+        <v>518919</v>
       </c>
       <c r="R44" t="n">
-        <v>6906358</v>
+        <v>6906309</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5249,7 +5250,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5259,7 +5260,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5286,7 +5287,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134665127</v>
+        <v>134665124</v>
       </c>
       <c r="B45" t="n">
         <v>80493</v>
@@ -5321,13 +5322,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518871</v>
+        <v>518888</v>
       </c>
       <c r="R45" t="n">
-        <v>6906383</v>
+        <v>6906358</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5356,7 +5357,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5366,7 +5367,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5393,32 +5394,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134665120</v>
+        <v>134665127</v>
       </c>
       <c r="B46" t="n">
-        <v>57896</v>
+        <v>80493</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100001</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5428,13 +5429,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518939</v>
+        <v>518871</v>
       </c>
       <c r="R46" t="n">
-        <v>6906345</v>
+        <v>6906383</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5463,7 +5464,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5473,19 +5474,14 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Risbo i grov asp där stammen förgrenar sig i ett Y.</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5505,10 +5501,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134665055</v>
+        <v>134665120</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>57896</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5516,16 +5512,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5534,27 +5530,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518813</v>
+        <v>518939</v>
       </c>
       <c r="R47" t="n">
-        <v>6906445</v>
+        <v>6906345</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5583,7 +5571,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5593,19 +5581,19 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Risbo i grov asp där stammen förgrenar sig i ett Y.</t>
         </is>
       </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG47" t="b">
         <v>0</v>
@@ -5625,7 +5613,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134665067</v>
+        <v>134665055</v>
       </c>
       <c r="B48" t="n">
         <v>57975</v>
@@ -5668,10 +5656,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518823</v>
+        <v>518813</v>
       </c>
       <c r="R48" t="n">
-        <v>6906410</v>
+        <v>6906445</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5703,7 +5691,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5713,12 +5701,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5745,7 +5733,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134665092</v>
+        <v>134665067</v>
       </c>
       <c r="B49" t="n">
         <v>57975</v>
@@ -5788,13 +5776,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518883</v>
+        <v>518823</v>
       </c>
       <c r="R49" t="n">
-        <v>6906465</v>
+        <v>6906410</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5823,7 +5811,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5833,7 +5821,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -5865,7 +5853,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134665099</v>
+        <v>134665092</v>
       </c>
       <c r="B50" t="n">
         <v>57975</v>
@@ -5908,13 +5896,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518878</v>
+        <v>518883</v>
       </c>
       <c r="R50" t="n">
-        <v>6906434</v>
+        <v>6906465</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5943,7 +5931,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5953,7 +5941,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -5985,7 +5973,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134665102</v>
+        <v>134665099</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -6028,10 +6016,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518913</v>
+        <v>518878</v>
       </c>
       <c r="R51" t="n">
-        <v>6906427</v>
+        <v>6906434</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6063,7 +6051,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6073,7 +6061,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6105,7 +6093,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134665123</v>
+        <v>134665102</v>
       </c>
       <c r="B52" t="n">
         <v>57975</v>
@@ -6148,13 +6136,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518891</v>
+        <v>518913</v>
       </c>
       <c r="R52" t="n">
-        <v>6906349</v>
+        <v>6906427</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6183,7 +6171,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6193,7 +6181,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6225,7 +6213,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134665125</v>
+        <v>134665123</v>
       </c>
       <c r="B53" t="n">
         <v>57975</v>
@@ -6258,7 +6246,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6268,13 +6256,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518880</v>
+        <v>518891</v>
       </c>
       <c r="R53" t="n">
-        <v>6906377</v>
+        <v>6906349</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6303,7 +6291,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6313,12 +6301,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6345,7 +6333,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134665130</v>
+        <v>134665125</v>
       </c>
       <c r="B54" t="n">
         <v>57975</v>
@@ -6378,7 +6366,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6388,13 +6376,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518852</v>
+        <v>518880</v>
       </c>
       <c r="R54" t="n">
-        <v>6906373</v>
+        <v>6906377</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6423,7 +6411,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6433,12 +6421,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6465,7 +6453,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134665131</v>
+        <v>134665130</v>
       </c>
       <c r="B55" t="n">
         <v>57975</v>
@@ -6493,20 +6481,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6516,13 +6496,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518823</v>
+        <v>518852</v>
       </c>
       <c r="R55" t="n">
-        <v>6906348</v>
+        <v>6906373</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6551,7 +6531,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6561,7 +6541,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6588,48 +6573,64 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134665047</v>
+        <v>134665131</v>
       </c>
       <c r="B56" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Grundvattsberget, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518802</v>
+        <v>518823</v>
       </c>
       <c r="R56" t="n">
-        <v>6906413</v>
+        <v>6906348</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6658,7 +6659,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6668,12 +6669,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>16 ex</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6700,7 +6696,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134665053</v>
+        <v>134665047</v>
       </c>
       <c r="B57" t="n">
         <v>99195</v>
@@ -6735,13 +6731,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518803</v>
+        <v>518802</v>
       </c>
       <c r="R57" t="n">
-        <v>6906438</v>
+        <v>6906413</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6770,7 +6766,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6780,12 +6776,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>16 ex</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6812,7 +6808,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134665059</v>
+        <v>134665053</v>
       </c>
       <c r="B58" t="n">
         <v>99195</v>
@@ -6847,13 +6843,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518826</v>
+        <v>518803</v>
       </c>
       <c r="R58" t="n">
-        <v>6906432</v>
+        <v>6906438</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6882,7 +6878,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6892,12 +6888,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6924,7 +6920,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134665080</v>
+        <v>134665059</v>
       </c>
       <c r="B59" t="n">
         <v>99195</v>
@@ -6959,10 +6955,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518830</v>
+        <v>518826</v>
       </c>
       <c r="R59" t="n">
-        <v>6906421</v>
+        <v>6906432</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6994,7 +6990,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7004,12 +7000,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>1 ex</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7036,7 +7032,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134665116</v>
+        <v>134665080</v>
       </c>
       <c r="B60" t="n">
         <v>99195</v>
@@ -7071,13 +7067,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518987</v>
+        <v>518830</v>
       </c>
       <c r="R60" t="n">
-        <v>6906384</v>
+        <v>6906421</v>
       </c>
       <c r="S60" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7106,7 +7102,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7116,12 +7112,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>1 ex</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7148,7 +7144,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134665119</v>
+        <v>134665116</v>
       </c>
       <c r="B61" t="n">
         <v>99195</v>
@@ -7183,13 +7179,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518975</v>
+        <v>518987</v>
       </c>
       <c r="R61" t="n">
-        <v>6906374</v>
+        <v>6906384</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7218,7 +7214,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7228,12 +7224,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7260,32 +7256,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134665110</v>
+        <v>134665119</v>
       </c>
       <c r="B62" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7295,13 +7291,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519040</v>
+        <v>518975</v>
       </c>
       <c r="R62" t="n">
-        <v>6906597</v>
+        <v>6906374</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7330,7 +7326,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7340,7 +7336,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7367,32 +7368,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134665034</v>
+        <v>134665110</v>
       </c>
       <c r="B63" t="n">
-        <v>80438</v>
+        <v>79131</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7402,13 +7403,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518772</v>
+        <v>519040</v>
       </c>
       <c r="R63" t="n">
-        <v>6906420</v>
+        <v>6906597</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7437,7 +7438,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7447,7 +7448,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7474,7 +7475,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134665071</v>
+        <v>134665034</v>
       </c>
       <c r="B64" t="n">
         <v>80438</v>
@@ -7509,13 +7510,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518829</v>
+        <v>518772</v>
       </c>
       <c r="R64" t="n">
-        <v>6906402</v>
+        <v>6906420</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7544,7 +7545,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7554,7 +7555,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7581,7 +7582,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134665096</v>
+        <v>134665071</v>
       </c>
       <c r="B65" t="n">
         <v>80438</v>
@@ -7616,13 +7617,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518886</v>
+        <v>518829</v>
       </c>
       <c r="R65" t="n">
-        <v>6906456</v>
+        <v>6906402</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7651,7 +7652,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7661,7 +7662,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7688,7 +7689,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134665117</v>
+        <v>134665096</v>
       </c>
       <c r="B66" t="n">
         <v>80438</v>
@@ -7723,13 +7724,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518968</v>
+        <v>518886</v>
       </c>
       <c r="R66" t="n">
-        <v>6906366</v>
+        <v>6906456</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7758,7 +7759,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7768,7 +7769,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7792,6 +7793,113 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134665117</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Grundvattsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>518968</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6906366</v>
+      </c>
+      <c r="S67" t="n">
+        <v>9</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24424-2026 artfynd.xlsx
+++ b/artfynd/A 24424-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665043</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665057</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665061</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665082</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665128</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665072</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665087</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665129</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665049</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665051</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665074</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665078</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665085</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665089</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665091</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665107</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2496,6 +2581,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665133</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2603,6 +2693,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665097</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2710,6 +2805,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665076</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2818,6 +2918,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665114</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2925,6 +3030,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665132</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3032,6 +3142,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665104</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3139,6 +3254,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665105</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3246,6 +3366,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665039</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3353,6 +3478,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665069</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3460,6 +3590,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665101</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3567,6 +3702,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665103</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3674,6 +3814,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665109</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3781,6 +3926,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665111</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3888,6 +4038,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665115</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3995,6 +4150,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665041</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4102,6 +4262,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665045</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4209,6 +4374,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665106</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4316,6 +4486,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665108</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4423,6 +4598,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665112</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4530,6 +4710,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665037</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4637,6 +4822,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665035</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4744,6 +4934,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665065</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4856,6 +5051,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665083</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4963,6 +5163,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665122</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5070,6 +5275,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665126</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5177,6 +5387,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665063</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5284,6 +5499,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665121</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5391,6 +5611,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665124</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5498,6 +5723,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665127</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5610,6 +5840,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665120</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5730,6 +5965,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665055</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5850,6 +6090,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665067</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5970,6 +6215,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665092</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6090,6 +6340,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665099</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6210,6 +6465,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665102</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6330,6 +6590,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665123</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6450,6 +6715,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665125</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6570,6 +6840,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665130</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6693,6 +6968,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665131</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6805,6 +7085,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665047</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6917,6 +7202,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665053</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7029,6 +7319,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665059</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7141,6 +7436,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665080</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7253,6 +7553,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665116</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7365,6 +7670,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665119</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7472,6 +7782,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665110</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7579,6 +7894,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665034</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7686,6 +8006,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665071</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7793,6 +8118,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665096</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7900,8 +8230,81 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665117</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>